--- a/public/绩效质量标准库.xlsx
+++ b/public/绩效质量标准库.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C74EF6E-7DD0-4D61-97DC-A03CD0AA4D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{048BEA0B-3BB3-4660-8CCA-B33DB3223059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
   <si>
     <t>类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -82,13 +82,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1.未按产品原型要求完成功能开发不得分，每遗漏一个功能扣5分，累计2个及以上不得分
-2.Bug未按时限修复（P0-P3等级定义及修复时效详见《客户/业务部门投诉衡量标准》)
-3.已开发功能因开发质量问题，造成已有功能异常、阻碍交付：扣5分/次
-4.投诉扣分标准详见《客户/业务部门投诉衡量标准》</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>功能优化</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -102,10 +95,6 @@
     <t>1.未按产品原型要求完成功能开发不得分，每遗漏一个功能扣5分，累计2个及以上不得分
 2.已优化功能因开发质量问题，造成已有功能异常、阻碍交付：扣5分/次；
 3.投诉扣分标准详见《客户/业务部门投诉衡量标准》</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技术分享/代码审查</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -261,6 +250,34 @@
     <t>1. 文档内容每缺失一项内容，扣3分
 2. 文档内容不具备实操指导价值，扣5分
 3. 投诉扣分标准详见《客户/业务部门投诉衡量标准》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.未按产品原型要求完成功能开发不得分，每遗漏一个功能扣5分，累计2个及以上不得分
+2.Bug未按时限修复（P0-P3等级定义及修复时效详见《客户/业务部门投诉衡量标准》)
+3.已开发功能因开发质量问题，造成已有功能异常、阻碍交付：扣10分/次
+4.投诉扣分标准详见《客户/业务部门投诉衡量标准》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技术分享</t>
+  </si>
+  <si>
+    <t>代码审查</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.结合智能派单功能完成AI大模型使用分享并输出文档
+2.满意度100%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.未完成分享不得分 
+2.内部投诉扣3分/次，外部投诉扣5分/次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -637,177 +654,236 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="46.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="54.125" customWidth="1"/>
-    <col min="3" max="3" width="54.75" customWidth="1"/>
+    <col min="2" max="2" width="46.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="54.125" customWidth="1"/>
+    <col min="4" max="4" width="54.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="9" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:4" s="9" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="2" customFormat="1" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:4" s="2" customFormat="1" ht="112.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="4" customFormat="1" ht="68.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="4" customFormat="1" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" s="4" customFormat="1" ht="68.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="4" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="4" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" s="4" customFormat="1" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+      <c r="B6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="4" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="4" customFormat="1" ht="157.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="4" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="4" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="5">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" s="4" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="3" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="5">
         <v>11</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="111" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="B13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="5">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" s="4" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" s="4" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C14" s="6" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" s="4" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="4" customFormat="1" ht="157.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" s="4" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" s="4" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" s="3" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
+      <c r="D14" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="5">
         <v>14</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="5">
         <v>15</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="111" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="93" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="7" t="s">
+      <c r="B16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="D16" s="7" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/public/绩效质量标准库.xlsx
+++ b/public/绩效质量标准库.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\self\ai-performance\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{048BEA0B-3BB3-4660-8CCA-B33DB3223059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D4F43C-B672-43DE-97DF-7C2ECEC14CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
   <si>
     <t>类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -278,6 +278,35 @@
   </si>
   <si>
     <t>序号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据清洗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.处理过程中收到内部投诉，扣2分/次,外部投诉5分/次
+2.数据清洗后，不满足系统使用，不得分
+3.投诉扣分标准详见《客户/业务部门投诉衡量标准》</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.完成XX数据清洗
+2.满意度100%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.根据产品原型完成功能模块测试，测试功能覆盖率100%；
+2.BUG有效率≥90%(即被开发驳回或标记为“不予解决/设计如此/无法复现/重复Bug”的Bug占比总bug数不超过10%)；
+3.开发已修复BUG，在规定时效内（P0/P1级8小时内，P2级2个工作日内）完成回归验证；
+4.满意度100%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.未按产品原型完成整体功能测试不得分，漏测功能扣3分/个；
+2.BUG有效率低于80%不得分，80%（含）-90%（不含）,每降低1%扣2分，（Bug有效率=(有效 Bug 数 ÷ 提交Bug总数)× 100%）；
+3.BUG验证时效详见《客户/业务部门投诉衡量标准》
+4.投诉扣分标准详见《客户/业务部门投诉衡量标准》</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -654,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="46.375" style="1" customWidth="1"/>
@@ -704,46 +733,46 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="4" customFormat="1" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" s="4" customFormat="1" ht="117.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="4" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="4" customFormat="1" ht="68.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="4" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="4" customFormat="1" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="4" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -751,27 +780,27 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="4" customFormat="1" ht="157.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="4" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="4" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -779,27 +808,27 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" s="4" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="4" customFormat="1" ht="157.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="4" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -807,82 +836,110 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" s="3" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="4" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="111" customHeight="1" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" s="4" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="3" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="111" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>36</v>
+        <v>15</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="93" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="5">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="5">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C18" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D18" s="7" t="s">
         <v>39</v>
       </c>
     </row>
